--- a/Data/C05 Figures.xlsx
+++ b/Data/C05 Figures.xlsx
@@ -11232,6 +11232,20 @@
         <v>3.66</v>
       </c>
     </row>
+    <row r="772">
+      <c r="A772" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B772" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="C772" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="D772" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C05 Figures.xlsx
+++ b/Data/C05 Figures.xlsx
@@ -11246,6 +11246,20 @@
         <v>3.73</v>
       </c>
     </row>
+    <row r="773">
+      <c r="A773" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B773" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="C773" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="D773" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C05 Figures.xlsx
+++ b/Data/C05 Figures.xlsx
@@ -11260,6 +11260,20 @@
         <v>3.72</v>
       </c>
     </row>
+    <row r="774">
+      <c r="A774" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B774" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="C774" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="D774" t="n">
+        <v>3.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
